--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99314</v>
+        <v>99324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99324</v>
+        <v>99325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99325</v>
+        <v>99330</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99330</v>
+        <v>99332</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99332</v>
+        <v>99338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99338</v>
+        <v>99350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99350</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99354</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 25838-2026 artfynd.xlsx
+++ b/artfynd/A 25838-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283203</v>
       </c>
       <c r="B2" t="n">
-        <v>99354</v>
+        <v>99358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
